--- a/TestData/LV_TMTT0038660_VerifyTheFunctionalityOfTimeRecordManagerForFVAStandardUserOntheSFLightningView.xlsx
+++ b/TestData/LV_TMTT0038660_VerifyTheFunctionalityOfTimeRecordManagerForFVAStandardUserOntheSFLightningView.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FE8B288-4709-4F2A-8CA7-2E7CE74BCC49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90FBF6DD-FC14-41AF-AEF6-B00A9FF31B85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="5" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="44">
   <si>
     <t>Global Search User</t>
   </si>
@@ -164,6 +164,18 @@
   </si>
   <si>
     <t>6</t>
+  </si>
+  <si>
+    <t>GroupName</t>
+  </si>
+  <si>
+    <t>Time Tracking PV</t>
+  </si>
+  <si>
+    <t>Profile</t>
+  </si>
+  <si>
+    <t>CF Financial User</t>
   </si>
 </sst>
 </file>
@@ -500,21 +512,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5703125" customWidth="1"/>
+    <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>34</v>
+      </c>
+      <c r="B2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_TMTT0038660_VerifyTheFunctionalityOfTimeRecordManagerForFVAStandardUserOntheSFLightningView.xlsx
+++ b/TestData/LV_TMTT0038660_VerifyTheFunctionalityOfTimeRecordManagerForFVAStandardUserOntheSFLightningView.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90FBF6DD-FC14-41AF-AEF6-B00A9FF31B85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{369EE68E-0B78-48B6-B113-6711D555C532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="5" r:id="rId1"/>
@@ -18,10 +18,7 @@
     <sheet name="ModuleName" sheetId="13" r:id="rId3"/>
     <sheet name="SummaryLogs" sheetId="7" r:id="rId4"/>
     <sheet name="DetailLogs" sheetId="11" r:id="rId5"/>
-    <sheet name="RateSheetManagement" sheetId="9" r:id="rId6"/>
-    <sheet name="StaffMember" sheetId="10" r:id="rId7"/>
-    <sheet name="UpdateData" sheetId="14" r:id="rId8"/>
-    <sheet name="Sheet2" sheetId="15" r:id="rId9"/>
+    <sheet name="UpdateData" sheetId="14" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="21">
   <si>
     <t>Global Search User</t>
   </si>
@@ -58,84 +55,9 @@
     <t>Conduct Analysis</t>
   </si>
   <si>
-    <t>TimeRecordManagerTitle</t>
-  </si>
-  <si>
-    <t>Time Record Period</t>
-  </si>
-  <si>
     <t>SummaryLogTIme</t>
   </si>
   <si>
-    <t>Engagement</t>
-  </si>
-  <si>
-    <t>Rate Sheet</t>
-  </si>
-  <si>
-    <t>Title</t>
-  </si>
-  <si>
-    <t>Manager, Information Services</t>
-  </si>
-  <si>
-    <t>Pnumber</t>
-  </si>
-  <si>
-    <t>Martin Zeller</t>
-  </si>
-  <si>
-    <t>Staff</t>
-  </si>
-  <si>
-    <t>8.0</t>
-  </si>
-  <si>
-    <t>Aaron Matthew Tsing Yinn Chinn</t>
-  </si>
-  <si>
-    <t>Financial Analyst</t>
-  </si>
-  <si>
-    <t>95.00</t>
-  </si>
-  <si>
-    <t>Terence Tchen</t>
-  </si>
-  <si>
-    <t>Senior Advisor</t>
-  </si>
-  <si>
-    <t>DefaultRateForAdminwithoutRatedSheetadded</t>
-  </si>
-  <si>
-    <t>DefaultRateForAdminwithRatedSheetadded</t>
-  </si>
-  <si>
-    <t>.00</t>
-  </si>
-  <si>
-    <t>(MEH) Thompson_CLP Toxicology-Thompson Hine, LLP-FVA-26495</t>
-  </si>
-  <si>
-    <t>Debevoise_Xie (Consulting)-Debevoise &amp; Plimpton LLP-FVA-26378</t>
-  </si>
-  <si>
-    <t>(GB) Anthony_ACOVA-Anthony Ostlund Baer &amp; Louwagie P.A.-FVA-27471</t>
-  </si>
-  <si>
-    <t>Eventide-Eventide Asset Management, LLC-FVA-111771</t>
-  </si>
-  <si>
-    <t>DRC - Original</t>
-  </si>
-  <si>
-    <t>Rahimeh Bahrampourian</t>
-  </si>
-  <si>
-    <t>Salesforce Administrator</t>
-  </si>
-  <si>
     <t>App Name</t>
   </si>
   <si>
@@ -154,9 +76,6 @@
     <t>Abax Credit Fund III-Abax Global Capital-FVA-104456</t>
   </si>
   <si>
-    <t>95</t>
-  </si>
-  <si>
     <t>8</t>
   </si>
   <si>
@@ -176,6 +95,15 @@
   </si>
   <si>
     <t>CF Financial User</t>
+  </si>
+  <si>
+    <t>Time Tracking Litigation</t>
+  </si>
+  <si>
+    <t>Prashant Kamath</t>
+  </si>
+  <si>
+    <t>Brevet PV-Brevet Capital-FVA-72676</t>
   </si>
 </sst>
 </file>
@@ -214,12 +142,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -231,7 +174,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -512,11 +455,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -524,21 +468,32 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>43</v>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -554,12 +509,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -577,12 +532,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -592,10 +547,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="61.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="48.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.5703125" customWidth="1"/>
     <col min="4" max="4" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -608,39 +563,38 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>22</v>
+      <c r="D2" s="2"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -651,7 +605,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48.42578125" bestFit="1" customWidth="1"/>
@@ -667,39 +621,38 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>22</v>
+      <c r="D2" s="2"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -709,131 +662,8 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="61.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="61.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="3">
-        <v>983</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="3">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="3">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C72E838B-CDBC-4DB0-BF1D-AC44E1CE047A}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
@@ -843,7 +673,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
@@ -851,22 +681,21 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>38</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA8B519D-B6C7-4E9E-B893-5442930BCAA2}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/TestData/LV_TMTT0038660_VerifyTheFunctionalityOfTimeRecordManagerForFVAStandardUserOntheSFLightningView.xlsx
+++ b/TestData/LV_TMTT0038660_VerifyTheFunctionalityOfTimeRecordManagerForFVAStandardUserOntheSFLightningView.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{369EE68E-0B78-48B6-B113-6711D555C532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D9DD94C-E0C8-4FC2-98F3-99E375B7A580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="5" r:id="rId1"/>
@@ -18,7 +18,8 @@
     <sheet name="ModuleName" sheetId="13" r:id="rId3"/>
     <sheet name="SummaryLogs" sheetId="7" r:id="rId4"/>
     <sheet name="DetailLogs" sheetId="11" r:id="rId5"/>
-    <sheet name="UpdateData" sheetId="14" r:id="rId6"/>
+    <sheet name="WeeklyOverview" sheetId="15" r:id="rId6"/>
+    <sheet name="UpdateData" sheetId="14" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="32">
   <si>
     <t>Global Search User</t>
   </si>
@@ -55,9 +56,6 @@
     <t>Conduct Analysis</t>
   </si>
   <si>
-    <t>SummaryLogTIme</t>
-  </si>
-  <si>
     <t>App Name</t>
   </si>
   <si>
@@ -100,10 +98,46 @@
     <t>Time Tracking Litigation</t>
   </si>
   <si>
-    <t>Prashant Kamath</t>
-  </si>
-  <si>
     <t>Brevet PV-Brevet Capital-FVA-72676</t>
+  </si>
+  <si>
+    <t>Time Tracking TFR</t>
+  </si>
+  <si>
+    <t>Time Tracking Beta</t>
+  </si>
+  <si>
+    <t>Aryan Singh</t>
+  </si>
+  <si>
+    <t>Andrew Ziegler</t>
+  </si>
+  <si>
+    <t>Abrams Capital – SP-Abrams Capital-FVA-107652</t>
+  </si>
+  <si>
+    <t>Andrew Proctor</t>
+  </si>
+  <si>
+    <t>Genesis Bank - Equity Valuation-Genesis Bank-FVA-123305</t>
+  </si>
+  <si>
+    <t>Project Beach - Tax-StoicLane-FVA-122317</t>
+  </si>
+  <si>
+    <t>NewTime</t>
+  </si>
+  <si>
+    <t>NewActivity</t>
+  </si>
+  <si>
+    <t>LogHours</t>
+  </si>
+  <si>
+    <t>Fieldwork</t>
+  </si>
+  <si>
+    <t>Closing/Bring Down</t>
   </si>
 </sst>
 </file>
@@ -142,7 +176,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -154,13 +188,71 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color indexed="64"/>
       </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -169,12 +261,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -455,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
@@ -463,37 +564,59 @@
     <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C2" s="6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="C3" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
+      <c r="C4" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -509,12 +632,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -532,12 +655,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -547,25 +670,25 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="48.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="53.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.5703125" customWidth="1"/>
-    <col min="4" max="4" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="44.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="44.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1"/>
@@ -573,13 +696,13 @@
       <c r="F1" s="1"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="A2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D2" s="2"/>
@@ -587,14 +710,39 @@
       <c r="F2" s="2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="3" t="s">
+      <c r="A3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="11" t="s">
         <v>3</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -605,7 +753,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48.42578125" bestFit="1" customWidth="1"/>
@@ -616,14 +764,14 @@
     <col min="6" max="6" width="44.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1"/>
@@ -631,13 +779,13 @@
       <c r="F1" s="1"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="A2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D2" s="2"/>
@@ -645,14 +793,39 @@
       <c r="F2" s="2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="3" t="s">
+      <c r="A3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="11" t="s">
         <v>3</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -662,37 +835,122 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{141FC8CB-EDDC-4BA3-A9B1-81628B43E4D1}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="53.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C72E838B-CDBC-4DB0-BF1D-AC44E1CE047A}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>12</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_TMTT0038660_VerifyTheFunctionalityOfTimeRecordManagerForFVAStandardUserOntheSFLightningView.xlsx
+++ b/TestData/LV_TMTT0038660_VerifyTheFunctionalityOfTimeRecordManagerForFVAStandardUserOntheSFLightningView.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D9DD94C-E0C8-4FC2-98F3-99E375B7A580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5D2D4BF-F89C-4DB5-9B60-BC646EEFFCBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="5" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="29">
   <si>
     <t>Global Search User</t>
   </si>
@@ -68,12 +68,6 @@
     <t>Time Record Manager</t>
   </si>
   <si>
-    <t>Cindy Ma</t>
-  </si>
-  <si>
-    <t>Abax Credit Fund III-Abax Global Capital-FVA-104456</t>
-  </si>
-  <si>
     <t>8</t>
   </si>
   <si>
@@ -86,9 +80,6 @@
     <t>GroupName</t>
   </si>
   <si>
-    <t>Time Tracking PV</t>
-  </si>
-  <si>
     <t>Profile</t>
   </si>
   <si>
@@ -113,12 +104,6 @@
     <t>Andrew Ziegler</t>
   </si>
   <si>
-    <t>Abrams Capital – SP-Abrams Capital-FVA-107652</t>
-  </si>
-  <si>
-    <t>Andrew Proctor</t>
-  </si>
-  <si>
     <t>Genesis Bank - Equity Valuation-Genesis Bank-FVA-123305</t>
   </si>
   <si>
@@ -138,6 +123,12 @@
   </si>
   <si>
     <t>Closing/Bring Down</t>
+  </si>
+  <si>
+    <t>Amy Xia</t>
+  </si>
+  <si>
+    <t>Debevoise_Xie (Compo Expert)-Debevoise &amp; Plimpton LLP-FVA-26522</t>
   </si>
 </sst>
 </file>
@@ -176,7 +167,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -200,19 +191,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -261,21 +239,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -556,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
@@ -565,58 +539,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="6" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>17</v>
-      </c>
       <c r="C3" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -670,7 +633,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53.7109375" bestFit="1" customWidth="1"/>
@@ -682,13 +645,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1" s="9" t="s">
+      <c r="B1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1"/>
@@ -696,53 +659,39 @@
       <c r="F1" s="1"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="13" t="s">
+      <c r="A2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="2"/>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="9" t="s">
         <v>3</v>
-      </c>
-      <c r="E3" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="9" t="s">
         <v>25</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -753,7 +702,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48.42578125" bestFit="1" customWidth="1"/>
@@ -765,13 +714,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1" s="9" t="s">
+      <c r="B1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1"/>
@@ -779,53 +728,39 @@
       <c r="F1" s="1"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="13" t="s">
+      <c r="A2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="2"/>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="9" t="s">
         <v>3</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="9" t="s">
         <v>25</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +771,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{141FC8CB-EDDC-4BA3-A9B1-81628B43E4D1}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53.7109375" bestFit="1" customWidth="1"/>
@@ -844,58 +779,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1" s="9" t="s">
+      <c r="B1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="13" t="s">
+      <c r="A2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="9" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="9" t="s">
         <v>25</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -905,7 +829,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C72E838B-CDBC-4DB0-BF1D-AC44E1CE047A}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
@@ -915,42 +839,34 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
